--- a/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>AIP</t>
   </si>
@@ -656,249 +656,261 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E8" s="3">
         <v>13300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>37900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10900</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1200</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1100</v>
       </c>
       <c r="G9" s="3">
         <v>1100</v>
       </c>
       <c r="H9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I9" s="3">
         <v>900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E10" s="3">
         <v>12000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>34200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,61 +930,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E12" s="3">
         <v>11000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>30800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7800</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,8 +1040,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1050,21 +1069,21 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>-1600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1077,8 +1096,11 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,8 +1152,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,114 +1173,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E17" s="3">
         <v>21700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>59600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8400</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-8700</v>
       </c>
       <c r="F18" s="3">
         <v>-8700</v>
       </c>
       <c r="G18" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="H18" s="3">
         <v>-9100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-21700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,8 +1307,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1284,43 +1317,43 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1328,50 +1361,53 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-20900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>5700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,8 +1417,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1390,17 +1429,17 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1455,8 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1434,96 +1473,102 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-8600</v>
+        <v>-9300</v>
       </c>
       <c r="E23" s="3">
         <v>-8600</v>
       </c>
       <c r="F23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="G23" s="3">
         <v>-8700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>300</v>
       </c>
       <c r="M24" s="3">
         <v>300</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1531,8 +1576,8 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1540,8 +1585,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1641,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-23400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1809,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1787,26 +1847,29 @@
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" s="3">
         <v>2800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-1200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1921,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,8 +1977,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1920,43 +1989,43 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -1964,61 +2033,67 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2145,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2286,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,41 +2308,42 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E41" s="3">
         <v>18600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>68200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>81300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>85800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11200</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,29 +2362,32 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E42" s="3">
         <v>27700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>28600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>32400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>30700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4400</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2314,8 +2403,8 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2329,41 +2418,44 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E43" s="3">
         <v>10400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2382,8 +2474,11 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2435,41 +2530,44 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E45" s="3">
         <v>5200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5100</v>
       </c>
       <c r="G45" s="3">
         <v>5100</v>
       </c>
       <c r="H45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I45" s="3">
         <v>8400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,41 +2586,44 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E46" s="3">
         <v>62000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>70400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>81100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>90700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>94900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>98900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>106600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24400</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,32 +2642,35 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E47" s="3">
         <v>19700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>16200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>17000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12200</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2582,8 +2686,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2594,40 +2698,43 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="E48" s="3">
         <v>7000</v>
       </c>
       <c r="F48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G48" s="3">
         <v>5200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4900</v>
-      </c>
-      <c r="K48" s="3">
-        <v>5200</v>
       </c>
       <c r="L48" s="3">
         <v>5200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
+      <c r="M48" s="3">
+        <v>5200</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
@@ -2647,41 +2754,44 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5700</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,8 +2810,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2866,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,41 +2922,44 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E52" s="3">
         <v>5200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,8 +2978,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,41 +3034,44 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>102800</v>
+      </c>
+      <c r="E54" s="3">
         <v>102200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>107300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>115500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>118800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>121200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>112400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>40600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3090,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3114,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,41 +3136,42 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3060,41 +3190,44 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="E58" s="3">
         <v>1600</v>
       </c>
       <c r="F58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1100</v>
-      </c>
-      <c r="J58" s="3">
-        <v>800</v>
       </c>
       <c r="K58" s="3">
         <v>800</v>
       </c>
       <c r="L58" s="3">
+        <v>800</v>
+      </c>
+      <c r="M58" s="3">
         <v>900</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3113,41 +3246,44 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E59" s="3">
         <v>42500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>41900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>38600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>41800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>40200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>39900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>38600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>39900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>34300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,41 +3302,44 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E60" s="3">
         <v>44500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>43700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>40900</v>
-      </c>
-      <c r="G60" s="3">
-        <v>43700</v>
       </c>
       <c r="H60" s="3">
         <v>43700</v>
       </c>
       <c r="I60" s="3">
+        <v>43700</v>
+      </c>
+      <c r="J60" s="3">
         <v>42500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>42500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>36700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,40 +3358,43 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>300</v>
-      </c>
-      <c r="G61" s="3">
-        <v>400</v>
       </c>
       <c r="H61" s="3">
         <v>400</v>
       </c>
       <c r="I61" s="3">
+        <v>400</v>
+      </c>
+      <c r="J61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>100</v>
-      </c>
-      <c r="K61" s="3">
-        <v>300</v>
       </c>
       <c r="L61" s="3">
         <v>300</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -3272,41 +3414,44 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E62" s="3">
         <v>34200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>34800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>34300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>34300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>32700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>24200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,8 +3470,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3526,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3582,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,41 +3638,44 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87700</v>
+      </c>
+      <c r="E66" s="3">
         <v>80100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>79900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>75500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>78000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>78500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>75400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>64700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>55600</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3694,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3718,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3772,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3828,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3694,11 +3861,11 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>5700</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -3717,8 +3884,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,41 +3940,44 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-103200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-92700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-84600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-75400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-66400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-59200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-51500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-45800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-39000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-31200</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +3996,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4052,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4108,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,41 +4164,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E76" s="3">
         <v>22000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>31800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>37500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>40400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>52900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-20700</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4035,8 +4220,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4276,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,47 +4417,48 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>800</v>
+      </c>
+      <c r="E83" s="3">
         <v>1000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>900</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4273,8 +4471,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4527,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4583,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4639,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4695,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,47 +4751,50 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>2200</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4591,8 +4807,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,47 +4831,48 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,8 +4885,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4941,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,47 +4997,50 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>-5100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +5053,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5077,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4898,8 +5131,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5187,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5243,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,47 +5299,50 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>76300</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5110,8 +5355,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5163,47 +5411,50 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>74100</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5214,6 +5465,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
   <si>
     <t>AIP</t>
   </si>
@@ -656,261 +656,274 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E8" s="3">
         <v>12500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>37900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10900</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1100</v>
       </c>
       <c r="H9" s="3">
         <v>1100</v>
       </c>
       <c r="I9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J9" s="3">
         <v>900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E10" s="3">
         <v>11100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>34200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,64 +944,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E12" s="3">
         <v>10700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>30800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7800</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1060,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1072,21 +1092,21 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>-1600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1099,8 +1119,11 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1155,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,120 +1200,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E17" s="3">
         <v>21800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>59600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15300</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-8700</v>
       </c>
       <c r="G18" s="3">
         <v>-8700</v>
       </c>
       <c r="H18" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-9100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,55 +1341,56 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1364,53 +1398,56 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-20900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>5700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1420,8 +1457,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1432,17 +1472,17 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1458,8 +1498,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1476,102 +1516,108 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9300</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-8600</v>
       </c>
       <c r="F23" s="3">
         <v>-8600</v>
       </c>
       <c r="G23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="H23" s="3">
         <v>-8700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-22300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4400</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>300</v>
       </c>
       <c r="N24" s="3">
         <v>300</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1579,8 +1625,8 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
@@ -1588,8 +1634,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,120 +1693,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-23400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4400</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-23400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4400</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1850,26 +1911,29 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3">
         <v>2800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-2600</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,55 +2047,58 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2036,64 +2106,70 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-23400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7000</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,125 +2224,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-23400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7000</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,44 +2395,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E41" s="3">
         <v>13700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>68200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>81300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>82200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>85800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,32 +2452,35 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E42" s="3">
         <v>27500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>27700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>28600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>32400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>30700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4400</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2406,8 +2496,8 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2421,8 +2511,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2430,35 +2523,35 @@
         <v>12300</v>
       </c>
       <c r="E43" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F43" s="3">
         <v>10400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2477,8 +2570,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2533,44 +2629,47 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E45" s="3">
         <v>4900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>5100</v>
       </c>
       <c r="H45" s="3">
         <v>5100</v>
       </c>
       <c r="I45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J45" s="3">
         <v>8400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,44 +2688,47 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E46" s="3">
         <v>58400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>62000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>70400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>75800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>81100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>90700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>94900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>98900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>106600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>24400</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,35 +2747,38 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E47" s="3">
         <v>21000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>16200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>17000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2794,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2701,43 +2806,46 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E48" s="3">
         <v>10000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>7000</v>
       </c>
       <c r="F48" s="3">
         <v>7000</v>
       </c>
       <c r="G48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H48" s="3">
         <v>5200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4900</v>
-      </c>
-      <c r="L48" s="3">
-        <v>5200</v>
       </c>
       <c r="M48" s="3">
         <v>5200</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>5200</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
@@ -2757,44 +2865,47 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E49" s="3">
         <v>8000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5700</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,8 +2924,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,44 +3042,47 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E52" s="3">
         <v>5300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,44 +3160,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E54" s="3">
         <v>102800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>102200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>106800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>107300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>115500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>118800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>121200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>112400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>120400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>40600</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,44 +3267,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,44 +3324,47 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1600</v>
       </c>
       <c r="F58" s="3">
         <v>1600</v>
       </c>
       <c r="G58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H58" s="3">
         <v>1200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>800</v>
       </c>
       <c r="L58" s="3">
         <v>800</v>
       </c>
       <c r="M58" s="3">
+        <v>800</v>
+      </c>
+      <c r="N58" s="3">
         <v>900</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3249,44 +3383,47 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E59" s="3">
         <v>44100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>41900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>38600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>41800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>40200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>39900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>39900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>34300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,44 +3442,47 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E60" s="3">
         <v>46400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>44500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>43700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>40900</v>
-      </c>
-      <c r="H60" s="3">
-        <v>43700</v>
       </c>
       <c r="I60" s="3">
         <v>43700</v>
       </c>
       <c r="J60" s="3">
+        <v>43700</v>
+      </c>
+      <c r="K60" s="3">
         <v>42500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>42500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>36700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,43 +3501,46 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>300</v>
-      </c>
-      <c r="H61" s="3">
-        <v>400</v>
       </c>
       <c r="I61" s="3">
         <v>400</v>
       </c>
       <c r="J61" s="3">
+        <v>400</v>
+      </c>
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>100</v>
-      </c>
-      <c r="L61" s="3">
-        <v>300</v>
       </c>
       <c r="M61" s="3">
         <v>300</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -3417,44 +3560,47 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E62" s="3">
         <v>40000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>34200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>34800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>34300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>33900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>34300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>32700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,44 +3796,47 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91800</v>
+      </c>
+      <c r="E66" s="3">
         <v>87700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>80100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>79900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>75500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>78000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>78500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>75400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>64700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>67500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3864,11 +4032,11 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>5700</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,44 +4114,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-112700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-103200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-92700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-84600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-75400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-66400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-59200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-51500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-45800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-39000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-31200</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,44 +4350,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E76" s="3">
         <v>15100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>31800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>37500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>40400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>52900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-20700</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,125 +4468,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-23400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7000</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4616,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4427,41 +4626,41 @@
         <v>800</v>
       </c>
       <c r="E83" s="3">
+        <v>800</v>
+      </c>
+      <c r="F83" s="3">
         <v>1000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>900</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4474,8 +4673,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,50 +4968,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>2200</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4810,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,50 +5052,51 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4888,8 +5109,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,50 +5227,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-30100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1400</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>-5100</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5056,8 +5286,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5134,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,50 +5545,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>76300</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,8 +5604,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5414,50 +5663,53 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-30800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>74100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>-2200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,6 +5720,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
   <si>
     <t>AIP</t>
   </si>
@@ -656,156 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E8" s="3">
         <v>12900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>37900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10900</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -813,117 +820,123 @@
         <v>1500</v>
       </c>
       <c r="E9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F9" s="3">
         <v>1400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1100</v>
       </c>
       <c r="I9" s="3">
         <v>1100</v>
       </c>
       <c r="J9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K9" s="3">
         <v>900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>900</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E10" s="3">
         <v>11400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>34200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,67 +958,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E12" s="3">
         <v>10800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>30800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7800</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,8 +1080,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1095,21 +1115,21 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1122,8 +1142,11 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,126 +1227,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E17" s="3">
         <v>22100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>59600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15300</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-8700</v>
       </c>
       <c r="H18" s="3">
         <v>-8700</v>
       </c>
       <c r="I18" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-9100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4400</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,58 +1375,59 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1401,56 +1435,59 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-20900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>5700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,8 +1497,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1475,17 +1515,17 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1501,8 +1541,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1519,108 +1559,114 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-8600</v>
       </c>
       <c r="G23" s="3">
         <v>-8600</v>
       </c>
       <c r="H23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-8700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-22300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4400</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
-      </c>
-      <c r="N24" s="3">
-        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>300</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1628,8 +1674,8 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -1637,8 +1683,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,126 +1745,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-23400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-23400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,31 +1931,34 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1914,26 +1975,29 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3">
         <v>2800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-1200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-2600</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,58 +2117,61 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2109,67 +2179,73 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-23400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7000</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,131 +2303,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-23400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7000</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,47 +2482,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E41" s="3">
         <v>26100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>68200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>81300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>82200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>85800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,35 +2542,38 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E42" s="3">
         <v>18700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>27500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>27700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>28600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>32400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>30700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4400</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2499,8 +2589,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2514,47 +2604,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>12300</v>
+        <v>8900</v>
       </c>
       <c r="E43" s="3">
         <v>12300</v>
       </c>
       <c r="F43" s="3">
+        <v>12300</v>
+      </c>
+      <c r="G43" s="3">
         <v>10400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2573,8 +2666,11 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2632,47 +2728,50 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E45" s="3">
         <v>4700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>5100</v>
       </c>
       <c r="I45" s="3">
         <v>5100</v>
       </c>
       <c r="J45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K45" s="3">
         <v>8400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5000</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,47 +2790,50 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E46" s="3">
         <v>61800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>58400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>62000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>70400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>75800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>81100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>90700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>94900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>98900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>106600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,38 +2852,41 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E47" s="3">
         <v>16300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>21000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>19700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>17000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>14200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2797,8 +2902,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -2809,46 +2914,49 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E48" s="3">
         <v>9300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>7000</v>
       </c>
       <c r="G48" s="3">
         <v>7000</v>
       </c>
       <c r="H48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I48" s="3">
         <v>5200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>5200</v>
       </c>
       <c r="N48" s="3">
         <v>5200</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>5200</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
@@ -2868,47 +2976,50 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E49" s="3">
         <v>7800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5700</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,8 +3038,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,47 +3162,50 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E52" s="3">
         <v>6100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3104,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,47 +3286,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E54" s="3">
         <v>101400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>102800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>102200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>106800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>107300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>115500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>118800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>121200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>112400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>40600</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,47 +3398,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3327,47 +3458,50 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
         <v>2000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1600</v>
       </c>
       <c r="G58" s="3">
         <v>1600</v>
       </c>
       <c r="H58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1100</v>
-      </c>
-      <c r="L58" s="3">
-        <v>800</v>
       </c>
       <c r="M58" s="3">
         <v>800</v>
       </c>
       <c r="N58" s="3">
+        <v>800</v>
+      </c>
+      <c r="O58" s="3">
         <v>900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3386,47 +3520,50 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E59" s="3">
         <v>47100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>44100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>42500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>41900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>38600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>41800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>40200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>39900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>38600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>34300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,47 +3582,50 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E60" s="3">
         <v>49800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>46400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>44500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>43700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>40900</v>
-      </c>
-      <c r="I60" s="3">
-        <v>43700</v>
       </c>
       <c r="J60" s="3">
         <v>43700</v>
       </c>
       <c r="K60" s="3">
+        <v>43700</v>
+      </c>
+      <c r="L60" s="3">
         <v>42500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>42500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>36700</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,46 +3644,49 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>300</v>
-      </c>
-      <c r="I61" s="3">
-        <v>400</v>
       </c>
       <c r="J61" s="3">
         <v>400</v>
       </c>
       <c r="K61" s="3">
+        <v>400</v>
+      </c>
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>100</v>
-      </c>
-      <c r="M61" s="3">
-        <v>300</v>
       </c>
       <c r="N61" s="3">
         <v>300</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3563,47 +3706,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E62" s="3">
         <v>40900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>40000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>34200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>34800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>34300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>33900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>32700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,47 +3954,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91100</v>
+      </c>
+      <c r="E66" s="3">
         <v>91800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>87700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>80100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>79900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>75500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>78000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>78500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>75400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>64700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4035,11 +4203,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>5700</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,47 +4288,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-121000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-112700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-103200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-92700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-84600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-75400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-66400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-59200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-51500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-45800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-39000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-31200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4176,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,47 +4536,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E76" s="3">
         <v>9500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>37500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>40400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>52900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-20700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,131 +4660,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-23400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7000</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,8 +4815,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4629,41 +4828,41 @@
         <v>800</v>
       </c>
       <c r="F83" s="3">
+        <v>800</v>
+      </c>
+      <c r="G83" s="3">
         <v>1000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
         <v>900</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4676,8 +4875,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,53 +5185,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>2200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5030,8 +5247,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,53 +5273,54 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5112,8 +5333,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,53 +5457,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E94" s="3">
         <v>11900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-30100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1400</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5289,8 +5519,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,53 +5791,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>76300</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5607,8 +5853,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5666,53 +5915,56 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E102" s="3">
         <v>12400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-30800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>74100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5723,6 +5975,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
   <si>
     <t>AIP</t>
   </si>
@@ -656,163 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E8" s="3">
         <v>14600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>37900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10900</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -823,120 +830,126 @@
         <v>1500</v>
       </c>
       <c r="F9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G9" s="3">
         <v>1400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1100</v>
       </c>
       <c r="J9" s="3">
         <v>1100</v>
       </c>
       <c r="K9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L9" s="3">
         <v>900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E10" s="3">
         <v>13100</v>
       </c>
-      <c r="E10" s="3">
-        <v>11400</v>
-      </c>
       <c r="F10" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G10" s="3">
         <v>11100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13500</v>
       </c>
-      <c r="I10" s="3">
-        <v>12100</v>
-      </c>
       <c r="J10" s="3">
+        <v>12000</v>
+      </c>
+      <c r="K10" s="3">
         <v>10100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>15800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,70 +972,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E12" s="3">
         <v>10700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>30800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7800</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1097,8 +1117,8 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>-2100</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1118,21 +1138,21 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>-1600</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1145,31 +1165,34 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E17" s="3">
         <v>22000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>59600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15300</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-9200</v>
       </c>
-      <c r="F18" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-8400</v>
-      </c>
       <c r="H18" s="3">
-        <v>-8700</v>
+        <v>-8500</v>
       </c>
       <c r="I18" s="3">
         <v>-8700</v>
       </c>
       <c r="J18" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-9100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4400</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,61 +1409,62 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
         <v>800</v>
       </c>
       <c r="K20" s="3">
+        <v>800</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1438,59 +1472,62 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6500</v>
       </c>
-      <c r="E21" s="3">
-        <v>-8100</v>
-      </c>
       <c r="F21" s="3">
-        <v>-8400</v>
+        <v>-9100</v>
       </c>
       <c r="G21" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="H21" s="3">
         <v>-7500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7900</v>
       </c>
-      <c r="I21" s="3">
-        <v>-8100</v>
-      </c>
       <c r="J21" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-7700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-20900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>5700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,8 +1537,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1518,17 +1558,17 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1544,8 +1584,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1562,114 +1602,120 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-8600</v>
       </c>
       <c r="H23" s="3">
         <v>-8600</v>
       </c>
       <c r="I23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="J23" s="3">
         <v>-8700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-22300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4400</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
-      </c>
-      <c r="O24" s="3">
-        <v>300</v>
       </c>
       <c r="P24" s="3">
         <v>300</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1677,8 +1723,8 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-23400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4400</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-23400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4400</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1960,8 +2021,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
@@ -1978,26 +2039,29 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3">
         <v>2800</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-2600</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,61 +2187,64 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>-800</v>
       </c>
       <c r="K32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2182,70 +2252,76 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-23400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7000</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-23400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7000</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,50 +2569,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E41" s="3">
         <v>22100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>37400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>81300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>82200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>85800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,38 +2632,41 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E42" s="3">
         <v>23600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>27500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>28600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>32400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>30700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4400</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2592,8 +2682,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2607,8 +2697,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2616,41 +2709,41 @@
         <v>8900</v>
       </c>
       <c r="E43" s="3">
-        <v>12300</v>
+        <v>9200</v>
       </c>
       <c r="F43" s="3">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="G43" s="3">
+        <v>12600</v>
+      </c>
+      <c r="H43" s="3">
         <v>10400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,31 +2762,34 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2731,50 +2827,53 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4200</v>
+        <v>2100</v>
       </c>
       <c r="E45" s="3">
-        <v>4700</v>
+        <v>2200</v>
       </c>
       <c r="F45" s="3">
-        <v>4900</v>
+        <v>2300</v>
       </c>
       <c r="G45" s="3">
-        <v>5200</v>
+        <v>3600</v>
       </c>
       <c r="H45" s="3">
-        <v>5900</v>
+        <v>2400</v>
       </c>
       <c r="I45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K45" s="3">
         <v>5100</v>
       </c>
-      <c r="J45" s="3">
-        <v>5100</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,50 +2892,53 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E46" s="3">
         <v>58900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>61800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>58400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>62000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>70400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>75800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>81100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>90700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>94900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>98900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>106600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24400</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,41 +2957,44 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E47" s="3">
         <v>15100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>16300</v>
       </c>
-      <c r="F47" s="3">
-        <v>21000</v>
-      </c>
       <c r="G47" s="3">
+        <v>20300</v>
+      </c>
+      <c r="H47" s="3">
         <v>19700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>17000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12200</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2905,8 +3010,8 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -2917,49 +3022,52 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E48" s="3">
         <v>8500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>7000</v>
       </c>
       <c r="H48" s="3">
         <v>7000</v>
       </c>
       <c r="I48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="J48" s="3">
         <v>5200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4900</v>
-      </c>
-      <c r="N48" s="3">
-        <v>5200</v>
       </c>
       <c r="O48" s="3">
         <v>5200</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>5200</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2979,50 +3087,53 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E49" s="3">
         <v>7600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,50 +3282,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6200</v>
+        <v>5600</v>
       </c>
       <c r="E52" s="3">
-        <v>6100</v>
+        <v>4900</v>
       </c>
       <c r="F52" s="3">
-        <v>5300</v>
+        <v>4500</v>
       </c>
       <c r="G52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="O52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P52" s="3">
         <v>5200</v>
       </c>
-      <c r="H52" s="3">
-        <v>4800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>3100</v>
-      </c>
-      <c r="L52" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M52" s="3">
-        <v>3100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>5200</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,50 +3412,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E54" s="3">
         <v>96400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>101400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>102800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>102200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>106800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>107300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>115500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>118800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>121200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>112400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>120400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>40600</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,50 +3529,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,50 +3592,53 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1100</v>
-      </c>
-      <c r="M58" s="3">
-        <v>800</v>
       </c>
       <c r="N58" s="3">
         <v>800</v>
       </c>
       <c r="O58" s="3">
+        <v>800</v>
+      </c>
+      <c r="P58" s="3">
         <v>900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,50 +3657,53 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>49500</v>
+        <v>39000</v>
       </c>
       <c r="E59" s="3">
-        <v>47100</v>
+        <v>36900</v>
       </c>
       <c r="F59" s="3">
-        <v>44100</v>
+        <v>33600</v>
       </c>
       <c r="G59" s="3">
-        <v>42500</v>
+        <v>33100</v>
       </c>
       <c r="H59" s="3">
-        <v>41900</v>
+        <v>29900</v>
       </c>
       <c r="I59" s="3">
+        <v>30400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>27800</v>
+      </c>
+      <c r="K59" s="3">
+        <v>41800</v>
+      </c>
+      <c r="L59" s="3">
+        <v>40200</v>
+      </c>
+      <c r="M59" s="3">
+        <v>39900</v>
+      </c>
+      <c r="N59" s="3">
         <v>38600</v>
       </c>
-      <c r="J59" s="3">
-        <v>41800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>40200</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>39900</v>
       </c>
-      <c r="M59" s="3">
-        <v>38600</v>
-      </c>
-      <c r="N59" s="3">
-        <v>39900</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,50 +3722,53 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E60" s="3">
         <v>51700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>46400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>44500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>43700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40900</v>
-      </c>
-      <c r="J60" s="3">
-        <v>43700</v>
       </c>
       <c r="K60" s="3">
         <v>43700</v>
       </c>
       <c r="L60" s="3">
+        <v>43700</v>
+      </c>
+      <c r="M60" s="3">
         <v>42500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>40400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>42500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>36700</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,49 +3787,52 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>900</v>
+        <v>4000</v>
       </c>
       <c r="E61" s="3">
-        <v>1100</v>
+        <v>4000</v>
       </c>
       <c r="F61" s="3">
-        <v>1300</v>
+        <v>4400</v>
       </c>
       <c r="G61" s="3">
-        <v>1400</v>
+        <v>4900</v>
       </c>
       <c r="H61" s="3">
-        <v>1300</v>
+        <v>2400</v>
       </c>
       <c r="I61" s="3">
-        <v>300</v>
+        <v>2500</v>
       </c>
       <c r="J61" s="3">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="K61" s="3">
         <v>400</v>
       </c>
       <c r="L61" s="3">
+        <v>400</v>
+      </c>
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>100</v>
-      </c>
-      <c r="N61" s="3">
-        <v>300</v>
       </c>
       <c r="O61" s="3">
         <v>300</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -3709,50 +3852,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>38500</v>
+        <v>2800</v>
       </c>
       <c r="E62" s="3">
-        <v>40900</v>
+        <v>2600</v>
       </c>
       <c r="F62" s="3">
-        <v>40000</v>
+        <v>2500</v>
       </c>
       <c r="G62" s="3">
-        <v>34200</v>
+        <v>1100</v>
       </c>
       <c r="H62" s="3">
-        <v>34800</v>
+        <v>1500</v>
       </c>
       <c r="I62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K62" s="3">
+        <v>33900</v>
+      </c>
+      <c r="L62" s="3">
         <v>34300</v>
       </c>
-      <c r="J62" s="3">
-        <v>33900</v>
-      </c>
-      <c r="K62" s="3">
-        <v>34300</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>32700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,50 +4112,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E66" s="3">
         <v>91100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>91800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>87700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>80100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>79900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>75500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>78000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>78500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>75400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>64700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55600</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4206,11 +4374,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>5700</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,50 +4462,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-128700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-121000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-112700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-103200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-92700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-84600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-75400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-66400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-59200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-51500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-45800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-39000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-31200</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,50 +4722,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E76" s="3">
         <v>5300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>37500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>40400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-20700</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-23400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7000</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,8 +5014,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4825,47 +5024,47 @@
         <v>800</v>
       </c>
       <c r="E83" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G83" s="3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
+        <v>400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3">
+        <v>500</v>
+      </c>
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
-        <v>600</v>
-      </c>
-      <c r="L83" s="3">
-        <v>500</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>900</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,56 +5402,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>2200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5250,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,8 +5494,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5283,47 +5504,47 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5336,8 +5557,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,56 +5687,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-30100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1400</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>-5100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5522,8 +5752,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,31 +5779,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,56 +6037,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>76300</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5856,31 +6102,34 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5918,56 +6167,59 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-30800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>74100</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>-2200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,6 +6230,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
   <si>
     <t>AIP</t>
   </si>
@@ -656,175 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E8" s="3">
         <v>14700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>37900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10900</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="E9" s="3">
         <v>1500</v>
@@ -833,123 +839,129 @@
         <v>1500</v>
       </c>
       <c r="G9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H9" s="3">
         <v>1400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1100</v>
       </c>
       <c r="K9" s="3">
         <v>1100</v>
       </c>
       <c r="L9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M9" s="3">
         <v>900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>900</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E10" s="3">
         <v>13300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>34200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>14000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,73 +985,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E12" s="3">
         <v>11900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>30800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7800</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,13 +1119,16 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-1900</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1117,12 +1136,12 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-2100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1141,21 +1160,21 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>-1600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1168,13 +1187,16 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E15" s="3">
         <v>800</v>
@@ -1186,17 +1208,17 @@
         <v>800</v>
       </c>
       <c r="H15" s="3">
+        <v>800</v>
+      </c>
+      <c r="I15" s="3">
         <v>1000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1233,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,8 +1280,9 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1264,129 +1290,135 @@
         <v>22600</v>
       </c>
       <c r="E17" s="3">
+        <v>22600</v>
+      </c>
+      <c r="F17" s="3">
         <v>22000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>22100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>59600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>27400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4400</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,64 +1442,65 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4000</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>800</v>
       </c>
       <c r="K20" s="3">
         <v>800</v>
       </c>
       <c r="L20" s="3">
+        <v>800</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1475,62 +1508,65 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-12400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-20900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>5700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,13 +1576,16 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1561,17 +1600,17 @@
         <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1587,8 +1626,8 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1605,120 +1644,126 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-8600</v>
       </c>
       <c r="I23" s="3">
         <v>-8600</v>
       </c>
       <c r="J23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="K23" s="3">
         <v>-8700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-22300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4400</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>300</v>
       </c>
       <c r="Q24" s="3">
         <v>300</v>
       </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1726,8 +1771,8 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
@@ -1735,8 +1780,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,138 +1848,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-23400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-23400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2024,8 +2084,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
@@ -2042,26 +2102,29 @@
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3">
         <v>2800</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-1200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-2600</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,64 +2256,67 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4000</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-800</v>
       </c>
       <c r="K32" s="3">
         <v>-800</v>
       </c>
       <c r="L32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2255,73 +2324,79 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-23400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,143 +2460,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-23400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,53 +2655,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E41" s="3">
         <v>17800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>28500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>37400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>68200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>81300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>82200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>85800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,41 +2721,44 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E42" s="3">
         <v>30800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>23600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>18700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>28600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>32400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>30700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4400</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2685,8 +2774,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2700,53 +2789,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E43" s="3">
         <v>8900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,8 +2857,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2791,8 +2886,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2830,53 +2925,56 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E45" s="3">
         <v>2100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,53 +2993,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E46" s="3">
         <v>62800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>58900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>61800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>58400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>62000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>70400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>75800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>81100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>90700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>94900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>98900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>106600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24400</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,44 +3061,47 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E47" s="3">
         <v>12300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>16300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>20300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>19700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>17000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12200</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3013,8 +3117,8 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3025,52 +3129,55 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E48" s="3">
         <v>8100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>7000</v>
       </c>
       <c r="I48" s="3">
         <v>7000</v>
       </c>
       <c r="J48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="K48" s="3">
         <v>5200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4900</v>
-      </c>
-      <c r="O48" s="3">
-        <v>5200</v>
       </c>
       <c r="P48" s="3">
         <v>5200</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>5200</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -3090,53 +3197,56 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E49" s="3">
         <v>7400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3155,8 +3265,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,53 +3401,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E52" s="3">
         <v>5600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3469,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,53 +3537,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E54" s="3">
         <v>97700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>96400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>101400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>102800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>102200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>106800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>107300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>115500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>118800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>121200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>112400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>120400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>40600</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,53 +3659,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,53 +3725,56 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1100</v>
-      </c>
-      <c r="N58" s="3">
-        <v>800</v>
       </c>
       <c r="O58" s="3">
         <v>800</v>
       </c>
       <c r="P58" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q58" s="3">
         <v>900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3660,53 +3793,56 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E59" s="3">
         <v>39000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>33600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>33100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>30400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>27800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>41800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>40200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>39900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>34300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,53 +3861,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E60" s="3">
         <v>54200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>51700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>49800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>46400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>44500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>43700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40900</v>
-      </c>
-      <c r="K60" s="3">
-        <v>43700</v>
       </c>
       <c r="L60" s="3">
         <v>43700</v>
       </c>
       <c r="M60" s="3">
+        <v>43700</v>
+      </c>
+      <c r="N60" s="3">
         <v>42500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>42500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36700</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,52 +3929,55 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="E61" s="3">
         <v>4000</v>
       </c>
       <c r="F61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G61" s="3">
         <v>4400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>400</v>
       </c>
       <c r="L61" s="3">
         <v>400</v>
       </c>
       <c r="M61" s="3">
+        <v>400</v>
+      </c>
+      <c r="N61" s="3">
         <v>200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>100</v>
-      </c>
-      <c r="O61" s="3">
-        <v>300</v>
       </c>
       <c r="P61" s="3">
         <v>300</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -3855,53 +3997,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
         <v>2800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>33900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3920,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,53 +4269,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>107300</v>
+      </c>
+      <c r="E66" s="3">
         <v>95500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>91100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>87700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>80100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>79900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>75500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>78000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>78500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>75400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>64700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>67500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4377,11 +4544,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>5700</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4400,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,53 +4635,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-136900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-128700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-121000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-112700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-103200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-92700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-84600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-75400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-66400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-59200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-51500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-45800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-39000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-31200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,53 +4907,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>31800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>47700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>52900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-20700</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,143 +5043,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-23400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,19 +5212,20 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>400</v>
       </c>
       <c r="G83" s="3">
         <v>400</v>
@@ -5039,35 +5237,35 @@
         <v>400</v>
       </c>
       <c r="J83" s="3">
+        <v>400</v>
+      </c>
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
         <v>900</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5080,8 +5278,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,59 +5618,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E89" s="3">
         <v>1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
         <v>2200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5470,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,59 +5714,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5560,8 +5780,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,59 +5916,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
         <v>-5100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5755,8 +5984,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5806,8 +6039,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5845,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,59 +6282,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>76300</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6105,8 +6350,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6131,8 +6379,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6170,59 +6418,62 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>74100</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
         <v>-2200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6233,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
   <si>
     <t>AIP</t>
   </si>
@@ -656,184 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E8" s="3">
         <v>15500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>37900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10900</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1600</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1500</v>
       </c>
       <c r="F9" s="3">
         <v>1500</v>
@@ -842,126 +849,132 @@
         <v>1500</v>
       </c>
       <c r="H9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I9" s="3">
         <v>1400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>1100</v>
       </c>
       <c r="L9" s="3">
         <v>1100</v>
       </c>
       <c r="M9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N9" s="3">
         <v>900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>900</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E10" s="3">
         <v>13900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>34200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>15800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>14000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10000</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,76 +999,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E12" s="3">
         <v>11500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>30800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7800</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,29 +1139,32 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1900</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-2100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1163,21 +1183,21 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>-1600</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1190,16 +1210,19 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>800</v>
+      </c>
+      <c r="E15" s="3">
         <v>900</v>
-      </c>
-      <c r="E15" s="3">
-        <v>800</v>
       </c>
       <c r="F15" s="3">
         <v>800</v>
@@ -1211,17 +1234,17 @@
         <v>800</v>
       </c>
       <c r="I15" s="3">
+        <v>800</v>
+      </c>
+      <c r="J15" s="3">
         <v>1000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1258,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,144 +1307,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>22600</v>
+        <v>24200</v>
       </c>
       <c r="E17" s="3">
         <v>22600</v>
       </c>
       <c r="F17" s="3">
+        <v>22600</v>
+      </c>
+      <c r="G17" s="3">
         <v>22000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>22100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>59600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15300</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-9100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4400</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,67 +1476,68 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>3400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4000</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>800</v>
       </c>
       <c r="L20" s="3">
         <v>800</v>
       </c>
       <c r="M20" s="3">
+        <v>800</v>
+      </c>
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1511,65 +1545,68 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-12400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>5700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,8 +1616,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1588,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1603,17 +1643,17 @@
         <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1629,8 +1669,8 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1647,126 +1687,132 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-8600</v>
       </c>
       <c r="J23" s="3">
         <v>-8600</v>
       </c>
       <c r="K23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="L23" s="3">
         <v>-8700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4400</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>300</v>
       </c>
       <c r="R24" s="3">
         <v>300</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1774,8 +1820,8 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
@@ -1783,8 +1829,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,144 +1900,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2087,8 +2148,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
@@ -2105,26 +2166,29 @@
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T29" s="3">
         <v>2800</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-1200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-2600</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,67 +2326,70 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4000</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-800</v>
       </c>
       <c r="L32" s="3">
         <v>-800</v>
       </c>
       <c r="M32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2327,76 +2397,82 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7000</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,149 +2539,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7000</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,56 +2742,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E41" s="3">
         <v>13700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>28500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>37400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>68200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>81300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>82200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>85800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,44 +2811,47 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E42" s="3">
         <v>30200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>30800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>23600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>18700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>27700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>28600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>32400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>30700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4400</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,8 +2867,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2792,56 +2882,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E43" s="3">
         <v>21100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8100</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +2953,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2889,8 +2985,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2928,56 +3024,59 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E45" s="3">
         <v>3500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,56 +3095,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E46" s="3">
         <v>69100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>62800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>58900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>61800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>58400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>62000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>70400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>75800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>81100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>90700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>94900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>98900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>106600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>24400</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,47 +3166,50 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E47" s="3">
         <v>14300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>20300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>19700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>16200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>17000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>14200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12200</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3120,8 +3225,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3132,55 +3237,58 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E48" s="3">
         <v>7900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>7000</v>
       </c>
       <c r="J48" s="3">
         <v>7000</v>
       </c>
       <c r="K48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="L48" s="3">
         <v>5200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4900</v>
-      </c>
-      <c r="P48" s="3">
-        <v>5200</v>
       </c>
       <c r="Q48" s="3">
         <v>5200</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="R48" s="3">
+        <v>5200</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
@@ -3200,56 +3308,59 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E49" s="3">
         <v>7200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5700</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3268,8 +3379,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,56 +3521,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E52" s="3">
         <v>5900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,56 +3663,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>98300</v>
+      </c>
+      <c r="E54" s="3">
         <v>106100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>97700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>96400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>101400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>102800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>102200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>106800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>107300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>115500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>118800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>121200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>112400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>120400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>40600</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,56 +3790,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3728,8 +3859,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3737,47 +3871,47 @@
         <v>2400</v>
       </c>
       <c r="E58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F58" s="3">
         <v>2100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1100</v>
-      </c>
-      <c r="O58" s="3">
-        <v>800</v>
       </c>
       <c r="P58" s="3">
         <v>800</v>
       </c>
       <c r="Q58" s="3">
+        <v>800</v>
+      </c>
+      <c r="R58" s="3">
         <v>900</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3796,56 +3930,59 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E59" s="3">
         <v>44200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>39000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>36900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>33600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>33100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>29900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>30400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>40200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>39900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>38600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>39900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>34300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,56 +4001,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E60" s="3">
         <v>59300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>54200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>51700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>49800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>46400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>44500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40900</v>
-      </c>
-      <c r="L60" s="3">
-        <v>43700</v>
       </c>
       <c r="M60" s="3">
         <v>43700</v>
       </c>
       <c r="N60" s="3">
+        <v>43700</v>
+      </c>
+      <c r="O60" s="3">
         <v>42500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>40400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>42500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36700</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,55 +4072,58 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E61" s="3">
         <v>3600</v>
-      </c>
-      <c r="E61" s="3">
-        <v>4000</v>
       </c>
       <c r="F61" s="3">
         <v>4000</v>
       </c>
       <c r="G61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H61" s="3">
         <v>4400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1500</v>
-      </c>
-      <c r="L61" s="3">
-        <v>400</v>
       </c>
       <c r="M61" s="3">
         <v>400</v>
       </c>
       <c r="N61" s="3">
+        <v>400</v>
+      </c>
+      <c r="O61" s="3">
         <v>200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>100</v>
-      </c>
-      <c r="P61" s="3">
-        <v>300</v>
       </c>
       <c r="Q61" s="3">
         <v>300</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -4000,56 +4143,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>33900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>34300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>32700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18600</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,56 +4427,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>103100</v>
+      </c>
+      <c r="E66" s="3">
         <v>107300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>95500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>91800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>87700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>80100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>79900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>75500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>78000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>78500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>75400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>64700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>67500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>55600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4547,11 +4715,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>5700</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4570,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,56 +4809,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-145000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-136900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-128700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-121000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-112700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-103200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-92700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-84600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-75400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-66400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-59200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-51500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-45800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-39000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-31200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4706,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,56 +5093,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>31800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>37500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>40400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-20700</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4978,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,149 +5235,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7000</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,8 +5411,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5222,13 +5421,13 @@
         <v>600</v>
       </c>
       <c r="E83" s="3">
+        <v>600</v>
+      </c>
+      <c r="F83" s="3">
         <v>800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>400</v>
       </c>
       <c r="H83" s="3">
         <v>400</v>
@@ -5240,35 +5439,35 @@
         <v>400</v>
       </c>
       <c r="K83" s="3">
+        <v>400</v>
+      </c>
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5281,8 +5480,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,62 +5835,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3">
         <v>2200</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5689,8 +5906,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,62 +5935,63 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5783,8 +6004,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,62 +6146,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>11900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
         <v>-5100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5987,8 +6217,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6042,8 +6276,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6081,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,62 +6528,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>76300</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
         <v>800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,8 +6599,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6382,8 +6631,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6421,62 +6670,65 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-30800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>74100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>-2200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,6 +6739,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>AIP</t>
   </si>
@@ -656,112 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -769,81 +773,84 @@
         <v>16500</v>
       </c>
       <c r="E8" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F8" s="3">
         <v>15500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10900</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1500</v>
       </c>
       <c r="G9" s="3">
         <v>1500</v>
@@ -852,129 +859,135 @@
         <v>1500</v>
       </c>
       <c r="I9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J9" s="3">
         <v>1400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1100</v>
       </c>
       <c r="M9" s="3">
         <v>1100</v>
       </c>
       <c r="N9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>900</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E10" s="3">
         <v>15000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>34200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>15800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>14000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,79 +1013,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E12" s="3">
         <v>11900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>30800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7800</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,32 +1159,35 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-2100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1186,21 +1206,21 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>-1600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,8 +1233,11 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1222,10 +1245,10 @@
         <v>800</v>
       </c>
       <c r="E15" s="3">
+        <v>800</v>
+      </c>
+      <c r="F15" s="3">
         <v>900</v>
-      </c>
-      <c r="F15" s="3">
-        <v>800</v>
       </c>
       <c r="G15" s="3">
         <v>800</v>
@@ -1237,17 +1260,17 @@
         <v>800</v>
       </c>
       <c r="J15" s="3">
+        <v>800</v>
+      </c>
+      <c r="K15" s="3">
         <v>1000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>600</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,150 +1334,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E17" s="3">
         <v>24200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>22600</v>
       </c>
       <c r="F17" s="3">
         <v>22600</v>
       </c>
       <c r="G17" s="3">
+        <v>22600</v>
+      </c>
+      <c r="H17" s="3">
         <v>22000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>21800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>59600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15300</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4400</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,70 +1510,71 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>3400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>800</v>
-      </c>
       <c r="I20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J20" s="3">
         <v>4000</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>800</v>
       </c>
       <c r="M20" s="3">
         <v>800</v>
       </c>
       <c r="N20" s="3">
+        <v>800</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1548,68 +1582,71 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N21" s="3">
         <v>-7700</v>
       </c>
-      <c r="E21" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-12400</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-20900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>5700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,8 +1656,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1631,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
         <v>100</v>
@@ -1646,17 +1686,17 @@
         <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1672,8 +1712,8 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1690,132 +1730,138 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-8600</v>
       </c>
       <c r="K23" s="3">
         <v>-8600</v>
       </c>
       <c r="L23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="M23" s="3">
         <v>-8700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-22300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4400</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>300</v>
       </c>
       <c r="S24" s="3">
         <v>300</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1823,8 +1869,8 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4400</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-23400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4400</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2151,8 +2212,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
@@ -2169,26 +2230,29 @@
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U29" s="3">
         <v>2800</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-1200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-2600</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,70 +2396,73 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>-800</v>
-      </c>
       <c r="I32" s="3">
+        <v>200</v>
+      </c>
+      <c r="J32" s="3">
         <v>-4000</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-800</v>
       </c>
       <c r="M32" s="3">
         <v>-800</v>
       </c>
       <c r="N32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2400,79 +2470,85 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,59 +2829,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E41" s="3">
         <v>16400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>37400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>68200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>81300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>82200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>85800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,47 +2901,50 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E42" s="3">
         <v>25900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>30200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>30800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>23600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>18700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>27500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>27700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>28600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>32400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>30700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4400</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2870,8 +2960,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2885,59 +2975,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>10300</v>
+        <v>18800</v>
       </c>
       <c r="E43" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F43" s="3">
         <v>21100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2988,8 +3084,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3027,8 +3123,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3036,50 +3135,50 @@
         <v>2300</v>
       </c>
       <c r="E45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F45" s="3">
         <v>3500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,59 +3197,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E46" s="3">
         <v>57400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>69100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>62800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>58900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>61800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>58400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>62000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>70400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>75800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>81100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>90700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>94900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>98900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>106600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,50 +3271,53 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E47" s="3">
         <v>17800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>15100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>19700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>17000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12200</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,8 +3333,8 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3240,58 +3345,61 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E48" s="3">
         <v>7800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>7000</v>
       </c>
       <c r="K48" s="3">
         <v>7000</v>
       </c>
       <c r="L48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="M48" s="3">
         <v>5200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4900</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>5200</v>
       </c>
       <c r="R48" s="3">
         <v>5200</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+      <c r="S48" s="3">
+        <v>5200</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -3311,59 +3419,62 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E49" s="3">
         <v>7000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5700</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,59 +3641,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E52" s="3">
         <v>6700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,59 +3789,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E54" s="3">
         <v>98300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>97700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>96400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>101400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>102800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>102200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>106800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>107300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>115500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>118800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>121200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>112400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>120400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40600</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,59 +3921,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,59 +3993,62 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2400</v>
+        <v>3100</v>
       </c>
       <c r="E58" s="3">
         <v>2400</v>
       </c>
       <c r="F58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G58" s="3">
         <v>2100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1100</v>
-      </c>
-      <c r="P58" s="3">
-        <v>800</v>
       </c>
       <c r="Q58" s="3">
         <v>800</v>
       </c>
       <c r="R58" s="3">
+        <v>800</v>
+      </c>
+      <c r="S58" s="3">
         <v>900</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,59 +4067,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E59" s="3">
         <v>40200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>44200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>39000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>36900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>33600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>33100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>29900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>30400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>41800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>40200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>39900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>38600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>39900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>34300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,59 +4141,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E60" s="3">
         <v>56500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>59300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>54200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>51700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>49800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>44500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40900</v>
-      </c>
-      <c r="M60" s="3">
-        <v>43700</v>
       </c>
       <c r="N60" s="3">
         <v>43700</v>
       </c>
       <c r="O60" s="3">
+        <v>43700</v>
+      </c>
+      <c r="P60" s="3">
         <v>42500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>40400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>42500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36700</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,58 +4215,61 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E61" s="3">
         <v>3900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3600</v>
-      </c>
-      <c r="F61" s="3">
-        <v>4000</v>
       </c>
       <c r="G61" s="3">
         <v>4000</v>
       </c>
       <c r="H61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I61" s="3">
         <v>4400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1500</v>
-      </c>
-      <c r="M61" s="3">
-        <v>400</v>
       </c>
       <c r="N61" s="3">
         <v>400</v>
       </c>
       <c r="O61" s="3">
+        <v>400</v>
+      </c>
+      <c r="P61" s="3">
         <v>200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>100</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>300</v>
       </c>
       <c r="R61" s="3">
         <v>300</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4146,59 +4289,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>33900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>34300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>32700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,59 +4585,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>114400</v>
+      </c>
+      <c r="E66" s="3">
         <v>103100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>107300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>95500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>91100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>91800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>87700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>80100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>79900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>75500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>78000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>78500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>75400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>64700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>67500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4718,11 +4886,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>5700</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,59 +4983,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-154100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-145000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-136900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-128700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-121000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-112700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-103200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-92700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-84600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-75400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-66400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-59200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-51500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-39000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-31200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,59 +5279,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-4800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>31800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>40400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>52900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-20700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,8 +5610,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5424,13 +5623,13 @@
         <v>600</v>
       </c>
       <c r="F83" s="3">
+        <v>600</v>
+      </c>
+      <c r="G83" s="3">
         <v>800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>400</v>
       </c>
       <c r="I83" s="3">
         <v>400</v>
@@ -5442,35 +5641,35 @@
         <v>400</v>
       </c>
       <c r="L83" s="3">
+        <v>400</v>
+      </c>
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1500</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
         <v>900</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,65 +6052,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E89" s="3">
         <v>2900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
         <v>2200</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,65 +6156,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,65 +6376,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>11900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-30100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1400</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
         <v>-5100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6279,8 +6513,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,65 +6774,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>76300</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
         <v>800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,8 +6848,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6634,8 +6883,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6673,65 +6922,68 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-30800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>74100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
         <v>-2200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6742,6 +6994,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>AIP</t>
   </si>
@@ -656,214 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E8" s="3">
         <v>17400</v>
-      </c>
-      <c r="E8" s="3">
-        <v>16500</v>
       </c>
       <c r="F8" s="3">
         <v>16500</v>
       </c>
       <c r="G8" s="3">
+        <v>16500</v>
+      </c>
+      <c r="H8" s="3">
         <v>15500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>37900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10900</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1600</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1500</v>
       </c>
       <c r="I9" s="3">
         <v>1500</v>
@@ -872,135 +878,141 @@
         <v>1500</v>
       </c>
       <c r="K9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L9" s="3">
         <v>1400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1200</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1100</v>
       </c>
       <c r="O9" s="3">
         <v>1100</v>
       </c>
       <c r="P9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E10" s="3">
         <v>15600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>14800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>34200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>15800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>14000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,85 +1040,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E12" s="3">
         <v>12600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>30800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7800</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,13 +1198,16 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-1500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1196,24 +1215,24 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>-1900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>-2100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1232,21 +1251,21 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
         <v>-1600</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,8 +1278,11 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1274,10 +1296,10 @@
         <v>800</v>
       </c>
       <c r="G15" s="3">
+        <v>800</v>
+      </c>
+      <c r="H15" s="3">
         <v>900</v>
-      </c>
-      <c r="H15" s="3">
-        <v>800</v>
       </c>
       <c r="I15" s="3">
         <v>800</v>
@@ -1289,17 +1311,17 @@
         <v>800</v>
       </c>
       <c r="L15" s="3">
+        <v>800</v>
+      </c>
+      <c r="M15" s="3">
         <v>1000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>600</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1336,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1387,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E17" s="3">
         <v>26100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>22600</v>
       </c>
       <c r="H17" s="3">
         <v>22600</v>
       </c>
       <c r="I17" s="3">
+        <v>22600</v>
+      </c>
+      <c r="J17" s="3">
         <v>22000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>59600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>27400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>15300</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-21700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,76 +1577,77 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>800</v>
       </c>
       <c r="O20" s="3">
         <v>800</v>
       </c>
       <c r="P20" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1622,74 +1655,77 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-9000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-20900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>5700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,13 +1735,16 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1717,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>100</v>
@@ -1732,17 +1771,17 @@
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1758,8 +1797,8 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1776,144 +1815,150 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9300</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-8600</v>
       </c>
       <c r="M23" s="3">
         <v>-8600</v>
       </c>
       <c r="N23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="O23" s="3">
         <v>-8700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-22300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>300</v>
       </c>
       <c r="U24" s="3">
         <v>300</v>
       </c>
       <c r="V24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1921,8 +1966,8 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
+      <c r="Y24" s="3">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
@@ -1930,8 +1975,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2055,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2279,8 +2339,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
@@ -2297,26 +2357,29 @@
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W29" s="3">
         <v>2800</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-1200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,76 +2535,79 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-800</v>
       </c>
       <c r="O32" s="3">
         <v>-800</v>
       </c>
       <c r="P32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2546,85 +2615,91 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2775,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,65 +3002,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E41" s="3">
         <v>17400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>28500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>37400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>68200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>81300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>82200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>85800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,53 +3080,56 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E42" s="3">
         <v>21600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>21900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>30200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>30800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>23600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>18700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>27500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>27700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>28600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>32400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>30700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,8 +3145,8 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3071,65 +3160,68 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E43" s="3">
         <v>16500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>18800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,8 +3240,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3186,8 +3281,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3225,65 +3320,68 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E45" s="3">
         <v>2500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2300</v>
       </c>
       <c r="F45" s="3">
         <v>2300</v>
       </c>
       <c r="G45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H45" s="3">
         <v>3500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5000</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,65 +3400,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>82400</v>
+      </c>
+      <c r="E46" s="3">
         <v>61000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>61500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>57400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>69100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>62800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>58900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>61800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>58400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>62000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>70400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>75800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>81100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>90700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>94900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>98900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>106600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>24400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,56 +3480,59 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E47" s="3">
         <v>21000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>15100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>16300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>19700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>16200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>17000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>14200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>12200</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,8 +3548,8 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3456,64 +3560,67 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>8700</v>
+        <v>7800</v>
       </c>
       <c r="E48" s="3">
         <v>8700</v>
       </c>
       <c r="F48" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G48" s="3">
         <v>7800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>7000</v>
       </c>
       <c r="M48" s="3">
         <v>7000</v>
       </c>
       <c r="N48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="O48" s="3">
         <v>5200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4900</v>
-      </c>
-      <c r="S48" s="3">
-        <v>5200</v>
       </c>
       <c r="T48" s="3">
         <v>5200</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>5200</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3533,65 +3640,68 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E49" s="3">
         <v>6500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5700</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3720,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,65 +3880,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E52" s="3">
         <v>8600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,65 +4040,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E54" s="3">
         <v>107700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>98300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>106100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>97700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>96400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>101400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>102800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>102200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>106800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>107300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>115500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>118800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>121200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>112400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>120400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>40600</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,65 +4182,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,65 +4260,68 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2400</v>
       </c>
       <c r="G58" s="3">
         <v>2400</v>
       </c>
       <c r="H58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I58" s="3">
         <v>2100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1100</v>
-      </c>
-      <c r="R58" s="3">
-        <v>800</v>
       </c>
       <c r="S58" s="3">
         <v>800</v>
       </c>
       <c r="T58" s="3">
+        <v>800</v>
+      </c>
+      <c r="U58" s="3">
         <v>900</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4207,65 +4340,68 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E59" s="3">
         <v>46200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>43300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>40200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>39000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>36900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>33600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>33100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>29900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>30400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>41800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>40200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>39900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>38600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>39900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>34300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,65 +4420,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E60" s="3">
         <v>66800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>62600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>56500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>59300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>54200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>51700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>49800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>46400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>44500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>43700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40900</v>
-      </c>
-      <c r="O60" s="3">
-        <v>43700</v>
       </c>
       <c r="P60" s="3">
         <v>43700</v>
       </c>
       <c r="Q60" s="3">
+        <v>43700</v>
+      </c>
+      <c r="R60" s="3">
         <v>42500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>40400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>42500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>36700</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,64 +4500,67 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E61" s="3">
         <v>4100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3600</v>
-      </c>
-      <c r="H61" s="3">
-        <v>4000</v>
       </c>
       <c r="I61" s="3">
         <v>4000</v>
       </c>
       <c r="J61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K61" s="3">
         <v>4400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1500</v>
-      </c>
-      <c r="O61" s="3">
-        <v>400</v>
       </c>
       <c r="P61" s="3">
         <v>400</v>
       </c>
       <c r="Q61" s="3">
+        <v>400</v>
+      </c>
+      <c r="R61" s="3">
         <v>200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>100</v>
-      </c>
-      <c r="S61" s="3">
-        <v>300</v>
       </c>
       <c r="T61" s="3">
         <v>300</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -4438,65 +4580,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>33900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>34300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>32700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>24200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18600</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,65 +4900,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>129700</v>
+      </c>
+      <c r="E66" s="3">
         <v>119200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>114400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>103100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>107300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>95500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>91100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>91800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>80100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>79900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>75500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>78000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>78500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>75400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>64700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>67500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>55600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5060,11 +5227,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>5700</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -5083,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,65 +5330,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-171600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-163100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-154100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-145000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-136900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-128700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-121000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-112700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-103200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-92700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-84600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-75400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-66400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-59200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-51500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-45800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-39000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-31200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,65 +5650,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-11400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-7500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-4800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>31800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>40400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>47700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>52900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-20700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5810,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,13 +6007,14 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
         <v>600</v>
@@ -5828,13 +6026,13 @@
         <v>600</v>
       </c>
       <c r="H83" s="3">
+        <v>600</v>
+      </c>
+      <c r="I83" s="3">
         <v>800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>400</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
@@ -5846,35 +6044,35 @@
         <v>400</v>
       </c>
       <c r="N83" s="3">
+        <v>400</v>
+      </c>
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1500</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3">
         <v>900</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5887,8 +6085,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,8 +6485,11 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6281,62 +6497,62 @@
         <v>3200</v>
       </c>
       <c r="E89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3">
         <v>2200</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6349,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,71 +6597,72 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6455,8 +6675,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,71 +6835,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>11900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-30100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1400</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3">
         <v>-5100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6686,8 +6915,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6753,8 +6986,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6792,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,71 +7265,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>76300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3">
         <v>800</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7100,8 +7345,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7138,8 +7386,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7177,71 +7425,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E102" s="3">
         <v>1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-30800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>74100</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3">
         <v>-2200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7252,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>AIP</t>
   </si>
@@ -656,223 +656,230 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E8" s="3">
         <v>20100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>16500</v>
       </c>
       <c r="G8" s="3">
         <v>16500</v>
       </c>
       <c r="H8" s="3">
+        <v>16500</v>
+      </c>
+      <c r="I8" s="3">
         <v>15500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>37900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>17500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10900</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1600</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1500</v>
       </c>
       <c r="J9" s="3">
         <v>1500</v>
@@ -881,138 +888,144 @@
         <v>1500</v>
       </c>
       <c r="L9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M9" s="3">
         <v>1400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1200</v>
-      </c>
-      <c r="O9" s="3">
-        <v>1100</v>
       </c>
       <c r="P9" s="3">
         <v>1100</v>
       </c>
       <c r="Q9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>900</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E10" s="3">
         <v>18300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>14800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>34200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>15800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>14000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10000</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,88 +1054,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E12" s="3">
         <v>13200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>30800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7800</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,41 +1218,44 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-2100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,21 +1274,21 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>-1600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1281,13 +1301,16 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="3">
         <v>800</v>
@@ -1299,10 +1322,10 @@
         <v>800</v>
       </c>
       <c r="H15" s="3">
+        <v>800</v>
+      </c>
+      <c r="I15" s="3">
         <v>900</v>
-      </c>
-      <c r="I15" s="3">
-        <v>800</v>
       </c>
       <c r="J15" s="3">
         <v>800</v>
@@ -1314,17 +1337,17 @@
         <v>800</v>
       </c>
       <c r="M15" s="3">
+        <v>800</v>
+      </c>
+      <c r="N15" s="3">
         <v>1000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>600</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1361,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,168 +1414,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E17" s="3">
         <v>28600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>26100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>22600</v>
       </c>
       <c r="I17" s="3">
         <v>22600</v>
       </c>
       <c r="J17" s="3">
+        <v>22600</v>
+      </c>
+      <c r="K17" s="3">
         <v>22000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>59600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>27400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15300</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-21700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,79 +1611,80 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>3300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>800</v>
       </c>
       <c r="P20" s="3">
         <v>800</v>
       </c>
       <c r="Q20" s="3">
+        <v>800</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
+      <c r="Z20" s="3">
+        <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
@@ -1658,77 +1692,80 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-10900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-20900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>5700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,17 +1775,20 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
@@ -1759,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1774,17 +1814,17 @@
         <v>100</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1800,8 +1840,8 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1818,150 +1858,156 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9300</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-8600</v>
       </c>
       <c r="N23" s="3">
         <v>-8600</v>
       </c>
       <c r="O23" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="P23" s="3">
         <v>-8700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-22300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-3700</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>300</v>
       </c>
       <c r="V24" s="3">
         <v>300</v>
       </c>
       <c r="W24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -1969,8 +2015,8 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
@@ -1978,8 +2024,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,168 +2107,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-23400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-23400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2342,8 +2403,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
@@ -2360,26 +2421,29 @@
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X29" s="3">
         <v>2800</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,79 +2605,82 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-800</v>
       </c>
       <c r="P32" s="3">
         <v>-800</v>
       </c>
       <c r="Q32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
+      <c r="Z32" s="3">
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
@@ -2618,88 +2688,94 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-23400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,173 +2854,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-23400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,68 +3089,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E41" s="3">
         <v>33900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>22100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>37400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>68200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>81300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>82200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>85800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,56 +3170,59 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E42" s="3">
         <v>20700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>21600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>21900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>25900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>30200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>30800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>23600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>27500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>27700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>28600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>32400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>30700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4400</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,8 +3238,8 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3163,68 +3253,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E43" s="3">
         <v>21100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>16500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3243,8 +3336,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3284,8 +3380,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3323,68 +3419,71 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E45" s="3">
         <v>5800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2300</v>
       </c>
       <c r="G45" s="3">
         <v>2300</v>
       </c>
       <c r="H45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I45" s="3">
         <v>3500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5000</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,68 +3502,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E46" s="3">
         <v>82400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>61000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>61500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>57400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>69100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>62800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>58900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>61800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>58400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>62000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>70400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>75800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>81100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>90700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>94900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>98900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>106600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>24400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,59 +3585,62 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E47" s="3">
         <v>7900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>21000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>20100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>17800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>15100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>19700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>16200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>17000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>14200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12200</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3551,8 +3656,8 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3563,67 +3668,70 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E48" s="3">
         <v>7800</v>
-      </c>
-      <c r="E48" s="3">
-        <v>8700</v>
       </c>
       <c r="F48" s="3">
         <v>8700</v>
       </c>
       <c r="G48" s="3">
+        <v>8700</v>
+      </c>
+      <c r="H48" s="3">
         <v>7800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>7000</v>
       </c>
       <c r="N48" s="3">
         <v>7000</v>
       </c>
       <c r="O48" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P48" s="3">
         <v>5200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4900</v>
-      </c>
-      <c r="T48" s="3">
-        <v>5200</v>
       </c>
       <c r="U48" s="3">
         <v>5200</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
+      <c r="V48" s="3">
+        <v>5200</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
@@ -3643,68 +3751,71 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E49" s="3">
         <v>6300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,8 +3834,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,68 +4000,71 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E52" s="3">
         <v>8200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3963,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,68 +4166,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>139900</v>
+      </c>
+      <c r="E54" s="3">
         <v>115000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>107700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>106900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>98300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>106100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>97700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>96400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>101400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>102800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>102200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>106800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>107300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>115500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>118800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>121200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>112400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>120400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>40600</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,68 +4313,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,68 +4394,71 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2400</v>
       </c>
       <c r="H58" s="3">
         <v>2400</v>
       </c>
       <c r="I58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J58" s="3">
         <v>2100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1100</v>
-      </c>
-      <c r="S58" s="3">
-        <v>800</v>
       </c>
       <c r="T58" s="3">
         <v>800</v>
       </c>
       <c r="U58" s="3">
+        <v>800</v>
+      </c>
+      <c r="V58" s="3">
         <v>900</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4343,68 +4477,71 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E59" s="3">
         <v>54800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>46200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>43300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>40200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>44200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>39000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>36900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>33600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>33100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>29900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>30400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>41800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>40200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>39900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>38600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>39900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>34300</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,68 +4560,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E60" s="3">
         <v>73200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>66800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>62600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>56500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>59300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>54200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>49800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>44500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>43700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>40900</v>
-      </c>
-      <c r="P60" s="3">
-        <v>43700</v>
       </c>
       <c r="Q60" s="3">
         <v>43700</v>
       </c>
       <c r="R60" s="3">
+        <v>43700</v>
+      </c>
+      <c r="S60" s="3">
         <v>42500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>40400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>42500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>36700</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,67 +4643,70 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3600</v>
-      </c>
-      <c r="I61" s="3">
-        <v>4000</v>
       </c>
       <c r="J61" s="3">
         <v>4000</v>
       </c>
       <c r="K61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L61" s="3">
         <v>4400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1500</v>
-      </c>
-      <c r="P61" s="3">
-        <v>400</v>
       </c>
       <c r="Q61" s="3">
         <v>400</v>
       </c>
       <c r="R61" s="3">
+        <v>400</v>
+      </c>
+      <c r="S61" s="3">
         <v>200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>100</v>
-      </c>
-      <c r="T61" s="3">
-        <v>300</v>
       </c>
       <c r="U61" s="3">
         <v>300</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -4583,68 +4726,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>34300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>32700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>24800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18600</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,68 +5058,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>137300</v>
+      </c>
+      <c r="E66" s="3">
         <v>129700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>119200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>114400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>103100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>107300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>95500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>91100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>91800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>87700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>80100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>79900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>75500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>78000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>78500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>75400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>64700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>67500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55600</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5230,11 +5398,11 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>5700</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5253,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,68 +5504,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-179600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-171600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-163100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-154100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-145000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-136900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-128700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-121000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-112700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-103200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-92700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-84600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-75400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-66400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-59200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-51500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-45800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-39000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-31200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,68 +5836,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-14600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-11400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-7500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-4800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>31800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>37500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>40400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>47700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>52900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-20700</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5733,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,173 +6002,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-23400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,16 +6206,17 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
-      </c>
-      <c r="E83" s="3">
-        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>600</v>
@@ -6029,13 +6228,13 @@
         <v>600</v>
       </c>
       <c r="I83" s="3">
+        <v>600</v>
+      </c>
+      <c r="J83" s="3">
         <v>800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
@@ -6047,35 +6246,35 @@
         <v>400</v>
       </c>
       <c r="O83" s="3">
+        <v>400</v>
+      </c>
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1500</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3">
         <v>900</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6088,8 +6287,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,74 +6702,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3200</v>
+        <v>-7100</v>
       </c>
       <c r="E89" s="3">
         <v>3200</v>
       </c>
       <c r="F89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G89" s="3">
         <v>-2500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3">
         <v>2200</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6568,8 +6785,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,74 +6818,75 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-100</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
       </c>
       <c r="T91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6899,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,74 +7065,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E94" s="3">
         <v>13100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>11900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-30100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3">
         <v>-5100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6918,8 +7148,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,8 +7181,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6989,8 +7223,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7028,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,74 +7511,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>76300</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3">
         <v>800</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7348,8 +7594,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7389,8 +7638,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7428,74 +7677,77 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="E102" s="3">
         <v>16400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-30800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>74100</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3">
         <v>-2200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7506,6 +7758,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
